--- a/Claude outputs/FBS Pay Progress Tracker 2.xlsx
+++ b/Claude outputs/FBS Pay Progress Tracker 2.xlsx
@@ -13,7 +13,7 @@
     <sheet state="visible" name="Plan calc" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -230,7 +230,7 @@
     <t>Login, password reset, roles and permissions</t>
   </si>
   <si>
-    <t xml:space="preserve">Backend live: Fortify login/forgot/reset, active-user middleware, 6 roles via Spatie. Capabilities updated (new reports.payroll.view, employees.bank.edit; HR admin limited to no payroll processing). Auth, security and profile feature tests exist. Role editing UI still on mock data. Oct 8: plans.ts and permissions.ts (RBAC) updated; Payroll Admin sidebar no longer shows an empty Settings header. Oct 8 review: status lowered from In testing to In progress. Only the frontend (mock data) exists; there is no working backend yet, so it cannot count as built-and-tested. Oct 9: backend permission-map API (PermissionMapController, role and capability resources) and UserPolicy added, with tests. Role editing screen still reads mock data, so left at In progress until it is wired.</t>
+    <t xml:space="preserve">Backend live: Fortify login/forgot/reset, active-user middleware, 6 roles via Spatie. Capabilities updated (new reports.payroll.view, employees.bank.edit; HR admin limited to no payroll processing). Auth, security and profile feature tests exist. Role editing UI still on mock data. Oct 8: plans.ts and permissions.ts (RBAC) updated; Payroll Admin sidebar no longer shows an empty Settings header. Oct 8 review: status lowered from In testing to In progress. Only the frontend (mock data) exists; there is no working backend yet, so it cannot count as built-and-tested. Oct 9: backend permission-map API (PermissionMapController, role and capability resources) and UserPolicy added, with tests. Oct 9 later: User Access role permissions dialog now reads the permission-map API (userAccessService); roles stay fixed per Spatie, so it is a read-only view. Moved to In testing: backend, UI and tests exist; tests not yet confirmed passing.</t>
   </si>
   <si>
     <t>T04</t>
@@ -239,7 +239,7 @@
     <t>User accounts, access and activity logs</t>
   </si>
   <si>
-    <t xml:space="preserve">User Access page (FE, mock) has permission catalog, userService and Activity Log panel. Oct 8: Users and Access routes and userService updated; Users page uses cards on mobile. Oct 9 backend: UserController API (list, create and invite, change role, activate/deactivate, resend invite, reset access) with queued, throttled invite emails; Activity Log API with filters and audit-trail columns; 19 user-management and 10 activity-log feature tests. Users and Access pages and userService still import mock data, so not wired to the API yet. Left at In progress; can move to In testing once wired.</t>
+    <t xml:space="preserve">User Access page (FE, mock) has permission catalog, userService and Activity Log panel. Oct 8: Users and Access routes and userService updated; Users page uses cards on mobile. Oct 9 backend: UserController API (list, create and invite, change role, activate/deactivate, resend invite, reset access) with queued, throttled invite emails; Activity Log API with filters and audit-trail columns; 19 user-management and 10 activity-log feature tests. Oct 9 later: Users and Access screen now wired to the API (new userAccessService and shared http client; useUsers hook, InviteUserDialog, RolePermissionsDialog, ActivityLogPanel). Activity log API gained more filters (11 tests now); Demo and User seeders updated. Moved to In testing: built end to end; tests not yet confirmed passing. Old mock userService only remains for employee profile and onboarding.</t>
   </si>
   <si>
     <t>T05</t>
@@ -4098,7 +4098,6 @@
     <row r="2" ht="25.5" customHeight="1">
       <c r="A2" s="3" t="str">
         <f>"Project Owner: "&amp;Tracker!C3&amp;"   |   "&amp;TEXT(Tracker!C4,"mmm d, yyyy")&amp;" to "&amp;TEXT(Tracker!C4+11*7-1,"mmm d, yyyy")&amp;"   |   11 weeks, "&amp;COUNTA(Tracker!A9:A31)&amp;" tasks"</f>
-        <v>Project Owner: Thea Consignado   |   Sep 15, 2026 to Nov 30, 2026   |   11 weeks, 23 tasks</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4130,44 +4129,36 @@
     <row r="5" ht="48.0" customHeight="1">
       <c r="A5" s="6">
         <f>Tracker!J32</f>
-        <v>0.4554973822</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="8">
         <f>Tracker!K32</f>
-        <v>0.387434555</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="9">
         <f>Tracker!L32</f>
-        <v>6.806282723</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="str">
         <f>COUNTIF(Tracker!I9:I31,"Done")&amp;" / "&amp;COUNTA(Tracker!A9:A31)</f>
-        <v>1 / 23</v>
       </c>
       <c r="H5" s="7"/>
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="11" t="str">
         <f>"Weighted by effort days"</f>
-        <v>Weighted by effort days</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="11" t="str">
         <f>IF(Tracker!C6=0,"Project has not started","Week "&amp;Tracker!C6&amp;" of 11")</f>
-        <v>Week 4 of 11</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="11" t="str">
         <f>IF(ABS(Tracker!L32)&lt;=2,"On plan",IF(Tracker!L32&gt;0,"Ahead of plan","Behind plan"))</f>
-        <v>Ahead of plan</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="11" t="str">
         <f>IF(Tracker!C6=0,"11 weeks to go",IF(11-Tracker!C6=0,"Final week",11-Tracker!C6&amp;" weeks left"))</f>
-        <v>7 weeks left</v>
       </c>
       <c r="H6" s="7"/>
     </row>
@@ -4224,7 +4215,7 @@
       </c>
       <c r="C11" s="22">
         <f>SUMPRODUCT((Tracker!$B$9:$B$31=A11)*Tracker!$F$9:$F$31*Tracker!$J$9:$J$31)/B11</f>
-        <v>0.5675675676</v>
+        <v>0.672972972972973</v>
       </c>
       <c r="D11" s="22">
         <f>SUMPRODUCT((Tracker!$B$9:$B$31=A11)*Tracker!$F$9:$F$31*Tracker!$K$9:$K$31)/B11</f>
@@ -4259,7 +4250,7 @@
       </c>
       <c r="G12" s="21">
         <f>COUNTIF(Tracker!$I$9:$I$31,F12)</f>
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
@@ -4283,7 +4274,7 @@
       </c>
       <c r="G13" s="21">
         <f>COUNTIF(Tracker!$I$9:$I$31,F13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" ht="21.75" customHeight="1">
@@ -4296,7 +4287,7 @@
       </c>
       <c r="C14" s="22">
         <f>SUMPRODUCT((Tracker!$B$9:$B$31=A14)*Tracker!$F$9:$F$31*Tracker!$J$9:$J$31)/B14</f>
-        <v>0.2708333333</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="D14" s="22">
         <f>SUMPRODUCT((Tracker!$B$9:$B$31=A14)*Tracker!$F$9:$F$31*Tracker!$K$9:$K$31)/B14</f>
@@ -4320,18 +4311,18 @@
       </c>
       <c r="C15" s="29">
         <f>Tracker!J32</f>
-        <v>0.4554973822</v>
+        <v>0.475916230366492</v>
       </c>
       <c r="D15" s="30">
         <f>Tracker!K32</f>
-        <v>0.387434555</v>
+        <v>0.387434554973822</v>
       </c>
       <c r="F15" s="31" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="32">
         <f>COUNTIF(Tracker!$M$9:$M$31,"Behind plan")</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" ht="24.0" customHeight="1">
@@ -5407,7 +5398,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;C3&amp;"   |   Tasks, schedule, and progress for the 11-week build, target finish Nov 30, 2026"</f>
-        <v>Project Owner: Thea Consignado   |   Tasks, schedule, and progress for the 11-week build, target finish Nov 30, 2026</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5451,7 +5441,7 @@
       </c>
       <c r="C5" s="41">
         <f>TODAY()</f>
-        <v>46304</v>
+        <v>46304.0</v>
       </c>
       <c r="E5" s="40" t="s">
         <v>32</v>
@@ -5539,11 +5529,11 @@
       </c>
       <c r="G9" s="47">
         <f t="shared" ref="G9:G31" si="1">$C$4+(D9-1)*7</f>
-        <v>46280</v>
+        <v>46280.0</v>
       </c>
       <c r="H9" s="47">
         <f t="shared" ref="H9:H31" si="2">$C$4+E9*7-1</f>
-        <v>46286</v>
+        <v>46286.0</v>
       </c>
       <c r="I9" s="48" t="s">
         <v>14</v>
@@ -5560,9 +5550,8 @@
         <f t="shared" ref="L9:L32" si="4">(J9-K9)*100</f>
         <v>0</v>
       </c>
-      <c r="M9" s="52" t="str">
+      <c r="M9" s="52">
         <f t="shared" ref="M9:M31" si="5">IF(AND($C$6&gt;0,J9&lt;1,K9-J9&gt;=0.25),"Behind plan","")</f>
-        <v/>
       </c>
       <c r="N9" s="45" t="s">
         <v>49</v>
@@ -5589,11 +5578,11 @@
       </c>
       <c r="G10" s="47">
         <f t="shared" si="1"/>
-        <v>46280</v>
+        <v>46280.0</v>
       </c>
       <c r="H10" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I10" s="53" t="s">
         <v>16</v>
@@ -5639,18 +5628,18 @@
       </c>
       <c r="G11" s="47">
         <f t="shared" si="1"/>
-        <v>46280</v>
+        <v>46280.0</v>
       </c>
       <c r="H11" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I11" s="53" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" s="49">
         <f>IFERROR(VLOOKUP(I11,Lists!$A$5:$B$8,2,FALSE()),0)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K11" s="50">
         <f t="shared" si="3"/>
@@ -5658,11 +5647,10 @@
       </c>
       <c r="L11" s="51">
         <f t="shared" si="4"/>
-        <v>-50</v>
-      </c>
-      <c r="M11" s="52" t="str">
+        <v>-20</v>
+      </c>
+      <c r="M11" s="52">
         <f t="shared" si="5"/>
-        <v>Behind plan</v>
       </c>
       <c r="N11" s="45" t="s">
         <v>55</v>
@@ -5689,18 +5677,18 @@
       </c>
       <c r="G12" s="47">
         <f t="shared" si="1"/>
-        <v>46287</v>
+        <v>46287.0</v>
       </c>
       <c r="H12" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J12" s="49">
         <f>IFERROR(VLOOKUP(I12,Lists!$A$5:$B$8,2,FALSE()),0)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K12" s="50">
         <f t="shared" si="3"/>
@@ -5708,11 +5696,10 @@
       </c>
       <c r="L12" s="51">
         <f t="shared" si="4"/>
-        <v>-50</v>
-      </c>
-      <c r="M12" s="52" t="str">
+        <v>-20</v>
+      </c>
+      <c r="M12" s="52">
         <f t="shared" si="5"/>
-        <v>Behind plan</v>
       </c>
       <c r="N12" s="45" t="s">
         <v>58</v>
@@ -5739,11 +5726,11 @@
       </c>
       <c r="G13" s="47">
         <f t="shared" si="1"/>
-        <v>46287</v>
+        <v>46287.0</v>
       </c>
       <c r="H13" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I13" s="53" t="s">
         <v>16</v>
@@ -5789,11 +5776,11 @@
       </c>
       <c r="G14" s="47">
         <f t="shared" si="1"/>
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="H14" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I14" s="53" t="s">
         <v>16</v>
@@ -5839,11 +5826,11 @@
       </c>
       <c r="G15" s="47">
         <f t="shared" si="1"/>
-        <v>46287</v>
+        <v>46287.0</v>
       </c>
       <c r="H15" s="47">
         <f t="shared" si="2"/>
-        <v>46300</v>
+        <v>46300.0</v>
       </c>
       <c r="I15" s="53" t="s">
         <v>16</v>
@@ -5889,11 +5876,11 @@
       </c>
       <c r="G16" s="47">
         <f t="shared" si="1"/>
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="H16" s="47">
         <f t="shared" si="2"/>
-        <v>46307</v>
+        <v>46307.0</v>
       </c>
       <c r="I16" s="53" t="s">
         <v>16</v>
@@ -5939,11 +5926,11 @@
       </c>
       <c r="G17" s="47">
         <f t="shared" si="1"/>
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="H17" s="47">
         <f t="shared" si="2"/>
-        <v>46307</v>
+        <v>46307.0</v>
       </c>
       <c r="I17" s="53" t="s">
         <v>16</v>
@@ -5989,11 +5976,11 @@
       </c>
       <c r="G18" s="47">
         <f t="shared" si="1"/>
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="H18" s="47">
         <f t="shared" si="2"/>
-        <v>46314</v>
+        <v>46314.0</v>
       </c>
       <c r="I18" s="53" t="s">
         <v>16</v>
@@ -6010,9 +5997,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M18" s="52" t="str">
+      <c r="M18" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N18" s="45" t="s">
         <v>76</v>
@@ -6039,11 +6025,11 @@
       </c>
       <c r="G19" s="47">
         <f t="shared" si="1"/>
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="H19" s="47">
         <f t="shared" si="2"/>
-        <v>46314</v>
+        <v>46314.0</v>
       </c>
       <c r="I19" s="53" t="s">
         <v>16</v>
@@ -6060,9 +6046,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M19" s="52" t="str">
+      <c r="M19" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N19" s="45" t="s">
         <v>79</v>
@@ -6089,11 +6074,11 @@
       </c>
       <c r="G20" s="47">
         <f t="shared" si="1"/>
-        <v>46308</v>
+        <v>46308.0</v>
       </c>
       <c r="H20" s="47">
         <f t="shared" si="2"/>
-        <v>46321</v>
+        <v>46321.0</v>
       </c>
       <c r="I20" s="53" t="s">
         <v>16</v>
@@ -6110,9 +6095,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M20" s="52" t="str">
+      <c r="M20" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N20" s="45" t="s">
         <v>82</v>
@@ -6139,11 +6123,11 @@
       </c>
       <c r="G21" s="47">
         <f t="shared" si="1"/>
-        <v>46308</v>
+        <v>46308.0</v>
       </c>
       <c r="H21" s="47">
         <f t="shared" si="2"/>
-        <v>46321</v>
+        <v>46321.0</v>
       </c>
       <c r="I21" s="53" t="s">
         <v>16</v>
@@ -6160,9 +6144,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M21" s="52" t="str">
+      <c r="M21" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N21" s="45" t="s">
         <v>85</v>
@@ -6189,11 +6172,11 @@
       </c>
       <c r="G22" s="47">
         <f t="shared" si="1"/>
-        <v>46308</v>
+        <v>46308.0</v>
       </c>
       <c r="H22" s="47">
         <f t="shared" si="2"/>
-        <v>46335</v>
+        <v>46335.0</v>
       </c>
       <c r="I22" s="53" t="s">
         <v>16</v>
@@ -6210,9 +6193,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M22" s="52" t="str">
+      <c r="M22" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N22" s="45" t="s">
         <v>88</v>
@@ -6239,11 +6221,11 @@
       </c>
       <c r="G23" s="47">
         <f t="shared" si="1"/>
-        <v>46322</v>
+        <v>46322.0</v>
       </c>
       <c r="H23" s="47">
         <f t="shared" si="2"/>
-        <v>46335</v>
+        <v>46335.0</v>
       </c>
       <c r="I23" s="53" t="s">
         <v>16</v>
@@ -6260,9 +6242,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M23" s="52" t="str">
+      <c r="M23" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N23" s="45" t="s">
         <v>91</v>
@@ -6289,11 +6270,11 @@
       </c>
       <c r="G24" s="47">
         <f t="shared" si="1"/>
-        <v>46322</v>
+        <v>46322.0</v>
       </c>
       <c r="H24" s="47">
         <f t="shared" si="2"/>
-        <v>46335</v>
+        <v>46335.0</v>
       </c>
       <c r="I24" s="53" t="s">
         <v>16</v>
@@ -6310,9 +6291,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M24" s="52" t="str">
+      <c r="M24" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N24" s="45" t="s">
         <v>94</v>
@@ -6339,11 +6319,11 @@
       </c>
       <c r="G25" s="47">
         <f t="shared" si="1"/>
-        <v>46315</v>
+        <v>46315.0</v>
       </c>
       <c r="H25" s="47">
         <f t="shared" si="2"/>
-        <v>46335</v>
+        <v>46335.0</v>
       </c>
       <c r="I25" s="53" t="s">
         <v>16</v>
@@ -6360,9 +6340,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M25" s="52" t="str">
+      <c r="M25" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N25" s="45" t="s">
         <v>97</v>
@@ -6389,11 +6368,11 @@
       </c>
       <c r="G26" s="47">
         <f t="shared" si="1"/>
-        <v>46329</v>
+        <v>46329.0</v>
       </c>
       <c r="H26" s="47">
         <f t="shared" si="2"/>
-        <v>46342</v>
+        <v>46342.0</v>
       </c>
       <c r="I26" s="53" t="s">
         <v>16</v>
@@ -6410,9 +6389,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M26" s="52" t="str">
+      <c r="M26" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N26" s="45" t="s">
         <v>100</v>
@@ -6439,11 +6417,11 @@
       </c>
       <c r="G27" s="47">
         <f t="shared" si="1"/>
-        <v>46315</v>
+        <v>46315.0</v>
       </c>
       <c r="H27" s="47">
         <f t="shared" si="2"/>
-        <v>46335</v>
+        <v>46335.0</v>
       </c>
       <c r="I27" s="53" t="s">
         <v>16</v>
@@ -6460,9 +6438,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M27" s="52" t="str">
+      <c r="M27" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N27" s="45" t="s">
         <v>103</v>
@@ -6489,11 +6466,11 @@
       </c>
       <c r="G28" s="47">
         <f t="shared" si="1"/>
-        <v>46336</v>
+        <v>46336.0</v>
       </c>
       <c r="H28" s="47">
         <f t="shared" si="2"/>
-        <v>46342</v>
+        <v>46342.0</v>
       </c>
       <c r="I28" s="53" t="s">
         <v>16</v>
@@ -6510,9 +6487,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M28" s="52" t="str">
+      <c r="M28" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N28" s="45" t="s">
         <v>106</v>
@@ -6539,11 +6515,11 @@
       </c>
       <c r="G29" s="47">
         <f t="shared" si="1"/>
-        <v>46336</v>
+        <v>46336.0</v>
       </c>
       <c r="H29" s="47">
         <f t="shared" si="2"/>
-        <v>46349</v>
+        <v>46349.0</v>
       </c>
       <c r="I29" s="53" t="s">
         <v>16</v>
@@ -6560,9 +6536,8 @@
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="M29" s="52" t="str">
+      <c r="M29" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N29" s="45" t="s">
         <v>109</v>
@@ -6589,11 +6564,11 @@
       </c>
       <c r="G30" s="47">
         <f t="shared" si="1"/>
-        <v>46336</v>
+        <v>46336.0</v>
       </c>
       <c r="H30" s="47">
         <f t="shared" si="2"/>
-        <v>46356</v>
+        <v>46356.0</v>
       </c>
       <c r="I30" s="53" t="s">
         <v>20</v>
@@ -6610,9 +6585,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M30" s="52" t="str">
+      <c r="M30" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N30" s="45" t="s">
         <v>112</v>
@@ -6639,11 +6613,11 @@
       </c>
       <c r="G31" s="47">
         <f t="shared" si="1"/>
-        <v>46343</v>
+        <v>46343.0</v>
       </c>
       <c r="H31" s="47">
         <f t="shared" si="2"/>
-        <v>46356</v>
+        <v>46356.0</v>
       </c>
       <c r="I31" s="53" t="s">
         <v>20</v>
@@ -6660,9 +6634,8 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M31" s="52" t="str">
+      <c r="M31" s="52">
         <f t="shared" si="5"/>
-        <v/>
       </c>
       <c r="N31" s="45" t="s">
         <v>115</v>
@@ -6678,22 +6651,20 @@
       <c r="E32" s="54"/>
       <c r="F32" s="28">
         <f>SUM(F9:F31)</f>
-        <v>191</v>
       </c>
       <c r="G32" s="54"/>
       <c r="H32" s="54"/>
       <c r="I32" s="54"/>
       <c r="J32" s="55">
         <f>SUMPRODUCT(F9:F31,J9:J31)/F32</f>
-        <v>0.4554973822</v>
       </c>
       <c r="K32" s="56">
         <f>SUMPRODUCT(F9:F31,K9:K31)/F32</f>
-        <v>0.387434555</v>
+        <v>0.387434554973822</v>
       </c>
       <c r="L32" s="57">
         <f t="shared" si="4"/>
-        <v>6.806282723</v>
+        <v>8.84816753926702</v>
       </c>
       <c r="M32" s="54"/>
       <c r="N32" s="54"/>
@@ -7794,7 +7765,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Light teal = scheduled weeks, dark teal = share complete, amber = current week"</f>
-        <v>Project Owner: Thea Consignado   |   Light teal = scheduled weeks, dark teal = share complete, amber = current week</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7898,62 +7868,61 @@
       </c>
       <c r="C5" s="70">
         <f>Tracker!$C$4+(C$4-1)*7</f>
-        <v>46280</v>
+        <v>46280.0</v>
       </c>
       <c r="D5" s="70">
         <f>Tracker!$C$4+(D$4-1)*7</f>
-        <v>46287</v>
+        <v>46287.0</v>
       </c>
       <c r="E5" s="70">
         <f>Tracker!$C$4+(E$4-1)*7</f>
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="F5" s="70">
         <f>Tracker!$C$4+(F$4-1)*7</f>
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="G5" s="70">
         <f>Tracker!$C$4+(G$4-1)*7</f>
-        <v>46308</v>
+        <v>46308.0</v>
       </c>
       <c r="H5" s="70">
         <f>Tracker!$C$4+(H$4-1)*7</f>
-        <v>46315</v>
+        <v>46315.0</v>
       </c>
       <c r="I5" s="70">
         <f>Tracker!$C$4+(I$4-1)*7</f>
-        <v>46322</v>
+        <v>46322.0</v>
       </c>
       <c r="J5" s="70">
         <f>Tracker!$C$4+(J$4-1)*7</f>
-        <v>46329</v>
+        <v>46329.0</v>
       </c>
       <c r="K5" s="70">
         <f>Tracker!$C$4+(K$4-1)*7</f>
-        <v>46336</v>
+        <v>46336.0</v>
       </c>
       <c r="L5" s="70">
         <f>Tracker!$C$4+(L$4-1)*7</f>
-        <v>46343</v>
+        <v>46343.0</v>
       </c>
       <c r="M5" s="70">
         <f>Tracker!$C$4+(M$4-1)*7</f>
-        <v>46350</v>
+        <v>46350.0</v>
       </c>
       <c r="N5" s="70">
         <f>Tracker!$C$4+(N$4-1)*7</f>
-        <v>46357</v>
+        <v>46357.0</v>
       </c>
       <c r="O5" s="70">
         <f>Tracker!$C$4+(O$4-1)*7</f>
-        <v>46364</v>
+        <v>46364.0</v>
       </c>
       <c r="P5" s="68"/>
     </row>
     <row r="6" ht="21.0" customHeight="1">
       <c r="A6" s="43" t="str">
         <f>Tracker!A9</f>
-        <v>T01</v>
       </c>
       <c r="B6" s="71" t="str">
         <f>Tracker!C9</f>
@@ -8097,7 +8066,7 @@
       </c>
       <c r="D8" s="72">
         <f>IF(AND(D$4&gt;=Tracker!$D11,D$4&lt;=Tracker!$E11),IF((D$4-Tracker!$D11+1)/(Tracker!$E11-Tracker!$D11+1)&lt;=Tracker!$J11+0.0001,2,1),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="72">
         <f>IF(AND(E$4&gt;=Tracker!$D11,E$4&lt;=Tracker!$E11),IF((E$4-Tracker!$D11+1)/(Tracker!$E11-Tracker!$D11+1)&lt;=Tracker!$J11+0.0001,2,1),0)</f>
@@ -8145,7 +8114,7 @@
       </c>
       <c r="P8" s="49">
         <f>Tracker!J11</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
@@ -8211,7 +8180,7 @@
       </c>
       <c r="P9" s="49">
         <f>Tracker!J12</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" ht="21.0" customHeight="1">
@@ -10494,7 +10463,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Enter Actual % at the end of each week (copy Tracker J32). Leave future weeks blank."</f>
-        <v>Project Owner: Thea Consignado   |   Enter Actual % at the end of each week (copy Tracker J32). Leave future weeks blank.</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10548,16 +10516,15 @@
       </c>
       <c r="B6" s="47">
         <f>Tracker!$C$4+(1-1)*7</f>
-        <v>46280</v>
+        <v>46280.0</v>
       </c>
       <c r="C6" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!D$4:D$26)/Tracker!$F$32</f>
-        <v>0.05410122164</v>
+        <v>0.0541012216404887</v>
       </c>
       <c r="D6" s="74"/>
       <c r="E6" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F6" s="71"/>
     </row>
@@ -10567,16 +10534,15 @@
       </c>
       <c r="B7" s="47">
         <f>Tracker!$C$4+(2-1)*7</f>
-        <v>46287</v>
+        <v>46287.0</v>
       </c>
       <c r="C7" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!E$4:E$26)/Tracker!$F$32</f>
-        <v>0.1369982548</v>
+        <v>0.136998254799302</v>
       </c>
       <c r="D7" s="74"/>
       <c r="E7" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F7" s="71"/>
     </row>
@@ -10586,16 +10552,15 @@
       </c>
       <c r="B8" s="47">
         <f>Tracker!$C$4+(3-1)*7</f>
-        <v>46294</v>
+        <v>46294.0</v>
       </c>
       <c r="C8" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!F$4:F$26)/Tracker!$F$32</f>
-        <v>0.2984293194</v>
+        <v>0.298429319371728</v>
       </c>
       <c r="D8" s="74"/>
       <c r="E8" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F8" s="71"/>
     </row>
@@ -10605,16 +10570,15 @@
       </c>
       <c r="B9" s="47">
         <f>Tracker!$C$4+(4-1)*7</f>
-        <v>46301</v>
+        <v>46301.0</v>
       </c>
       <c r="C9" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!G$4:G$26)/Tracker!$F$32</f>
-        <v>0.387434555</v>
+        <v>0.387434554973822</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F9" s="71"/>
     </row>
@@ -10624,16 +10588,15 @@
       </c>
       <c r="B10" s="47">
         <f>Tracker!$C$4+(5-1)*7</f>
-        <v>46308</v>
+        <v>46308.0</v>
       </c>
       <c r="C10" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!H$4:H$26)/Tracker!$F$32</f>
-        <v>0.4790575916</v>
+        <v>0.479057591623037</v>
       </c>
       <c r="D10" s="74"/>
       <c r="E10" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F10" s="71"/>
     </row>
@@ -10643,16 +10606,15 @@
       </c>
       <c r="B11" s="47">
         <f>Tracker!$C$4+(6-1)*7</f>
-        <v>46315</v>
+        <v>46315.0</v>
       </c>
       <c r="C11" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!I$4:I$26)/Tracker!$F$32</f>
-        <v>0.5689354276</v>
+        <v>0.568935427574171</v>
       </c>
       <c r="D11" s="74"/>
       <c r="E11" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F11" s="71"/>
     </row>
@@ -10662,16 +10624,15 @@
       </c>
       <c r="B12" s="47">
         <f>Tracker!$C$4+(7-1)*7</f>
-        <v>46322</v>
+        <v>46322.0</v>
       </c>
       <c r="C12" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!J$4:J$26)/Tracker!$F$32</f>
-        <v>0.6588132635</v>
+        <v>0.658813263525305</v>
       </c>
       <c r="D12" s="74"/>
       <c r="E12" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F12" s="71"/>
     </row>
@@ -10681,16 +10642,15 @@
       </c>
       <c r="B13" s="47">
         <f>Tracker!$C$4+(8-1)*7</f>
-        <v>46329</v>
+        <v>46329.0</v>
       </c>
       <c r="C13" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!K$4:K$26)/Tracker!$F$32</f>
-        <v>0.7748691099</v>
+        <v>0.774869109947644</v>
       </c>
       <c r="D13" s="74"/>
       <c r="E13" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F13" s="71"/>
     </row>
@@ -10700,16 +10660,15 @@
       </c>
       <c r="B14" s="47">
         <f>Tracker!$C$4+(9-1)*7</f>
-        <v>46336</v>
+        <v>46336.0</v>
       </c>
       <c r="C14" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!L$4:L$26)/Tracker!$F$32</f>
-        <v>0.8935427574</v>
+        <v>0.893542757417103</v>
       </c>
       <c r="D14" s="74"/>
       <c r="E14" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F14" s="71"/>
     </row>
@@ -10719,16 +10678,15 @@
       </c>
       <c r="B15" s="47">
         <f>Tracker!$C$4+(10-1)*7</f>
-        <v>46343</v>
+        <v>46343.0</v>
       </c>
       <c r="C15" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!M$4:M$26)/Tracker!$F$32</f>
-        <v>0.9546247818</v>
+        <v>0.954624781849913</v>
       </c>
       <c r="D15" s="74"/>
       <c r="E15" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F15" s="71"/>
     </row>
@@ -10738,7 +10696,7 @@
       </c>
       <c r="B16" s="47">
         <f>Tracker!$C$4+(11-1)*7</f>
-        <v>46350</v>
+        <v>46350.0</v>
       </c>
       <c r="C16" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!N$4:N$26)/Tracker!$F$32</f>
@@ -10747,7 +10705,6 @@
       <c r="D16" s="74"/>
       <c r="E16" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F16" s="71"/>
     </row>
@@ -10757,7 +10714,7 @@
       </c>
       <c r="B17" s="47">
         <f>Tracker!$C$4+(12-1)*7</f>
-        <v>46357</v>
+        <v>46357.0</v>
       </c>
       <c r="C17" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!O$4:O$26)/Tracker!$F$32</f>
@@ -10766,7 +10723,6 @@
       <c r="D17" s="74"/>
       <c r="E17" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F17" s="71"/>
     </row>
@@ -10776,7 +10732,7 @@
       </c>
       <c r="B18" s="47">
         <f>Tracker!$C$4+(13-1)*7</f>
-        <v>46364</v>
+        <v>46364.0</v>
       </c>
       <c r="C18" s="22">
         <f>SUMPRODUCT(Tracker!$F$9:$F$31,'Plan calc'!P$4:P$26)/Tracker!$F$32</f>
@@ -10785,7 +10741,6 @@
       <c r="D18" s="74"/>
       <c r="E18" s="75" t="str">
         <f t="shared" si="1"/>
-        <v/>
       </c>
       <c r="F18" s="71"/>
     </row>
@@ -11827,7 +11782,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Pick a Story status from the dropdown; Progress % is calculated from it"</f>
-        <v>Project Owner: Thea Consignado   |   Pick a Story status from the dropdown; Progress % is calculated from it</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11895,7 +11849,7 @@
       </c>
       <c r="H5" s="83" t="str">
         <f t="array" ref="H5">IFERROR(INDEX(Tracker!$I$9:$I$31,MATCH(G5,Tracker!$A$9:$A$31,0)),"")</f>
-        <v>In progress</v>
+        <v>In testing</v>
       </c>
       <c r="I5" s="84" t="s">
         <v>16</v>
@@ -11929,7 +11883,7 @@
       </c>
       <c r="H6" s="83" t="str">
         <f t="array" ref="H6">IFERROR(INDEX(Tracker!$I$9:$I$31,MATCH(G6,Tracker!$A$9:$A$31,0)),"")</f>
-        <v>In progress</v>
+        <v>In testing</v>
       </c>
       <c r="I6" s="84" t="s">
         <v>16</v>
@@ -11963,14 +11917,14 @@
       </c>
       <c r="H7" s="83" t="str">
         <f t="array" ref="H7">IFERROR(INDEX(Tracker!$I$9:$I$31,MATCH(G7,Tracker!$A$9:$A$31,0)),"")</f>
-        <v>In progress</v>
+        <v>In testing</v>
       </c>
       <c r="I7" s="84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J7" s="85">
         <f>IFERROR(VLOOKUP(I7,Lists!$A$5:$B$8,2,FALSE()),0)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" ht="34.5" customHeight="1">
@@ -11997,14 +11951,14 @@
       </c>
       <c r="H8" s="83" t="str">
         <f t="array" ref="H8">IFERROR(INDEX(Tracker!$I$9:$I$31,MATCH(G8,Tracker!$A$9:$A$31,0)),"")</f>
-        <v>In progress</v>
+        <v>In testing</v>
       </c>
       <c r="I8" s="84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J8" s="85">
         <f>IFERROR(VLOOKUP(I8,Lists!$A$5:$B$8,2,FALSE()),0)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="48.0" customHeight="1">
@@ -12031,14 +11985,14 @@
       </c>
       <c r="H9" s="83" t="str">
         <f t="array" ref="H9">IFERROR(INDEX(Tracker!$I$9:$I$31,MATCH(G9,Tracker!$A$9:$A$31,0)),"")</f>
-        <v>In progress</v>
+        <v>In testing</v>
       </c>
       <c r="I9" s="84" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J9" s="85">
         <f>IFERROR(VLOOKUP(I9,Lists!$A$5:$B$8,2,FALSE()),0)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" ht="34.5" customHeight="1">
@@ -14488,7 +14442,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Counts and progress of the user stories (linked to the User Stories sheet)"</f>
-        <v>Project Owner: Thea Consignado   |   Counts and progress of the user stories (linked to the User Stories sheet)</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14564,7 +14517,7 @@
       </c>
       <c r="B10" s="87">
         <f>AVERAGE('User Stories'!$J$5:$J$50)</f>
-        <v>0.4782608696</v>
+        <v>0.497826086956522</v>
       </c>
     </row>
     <row r="13" ht="24.0" customHeight="1">
@@ -14595,7 +14548,7 @@
       </c>
       <c r="C15" s="50">
         <f>IFERROR(SUMIFS('User Stories'!$J$5:$J$50,'User Stories'!$B$5:$B$50,A15)/B15,0)</f>
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="16">
@@ -15754,7 +15707,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Used by the Tracker and User Stories status dropdowns"</f>
-        <v>Project Owner: Thea Consignado   |   Used by the Tracker and User Stories status dropdowns</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -16853,7 +16805,6 @@
     <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="35" t="str">
         <f>"Project Owner: "&amp;Tracker!$C$3&amp;"   |   Planned fraction of each task complete by the end of each week, assuming even effort across its weeks"</f>
-        <v>Project Owner: Thea Consignado   |   Planned fraction of each task complete by the end of each week, assuming even effort across its weeks</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -17002,11 +16953,11 @@
       </c>
       <c r="D5" s="50">
         <f>MAX(0,MIN(1,(D$3-Tracker!$D10+1)/(Tracker!$E10-Tracker!$D10+1)))</f>
-        <v>0.3333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E5" s="50">
         <f>MAX(0,MIN(1,(E$3-Tracker!$D10+1)/(Tracker!$E10-Tracker!$D10+1)))</f>
-        <v>0.6666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="F5" s="50">
         <f>MAX(0,MIN(1,(F$3-Tracker!$D10+1)/(Tracker!$E10-Tracker!$D10+1)))</f>
@@ -17068,11 +17019,11 @@
       </c>
       <c r="D6" s="50">
         <f>MAX(0,MIN(1,(D$3-Tracker!$D11+1)/(Tracker!$E11-Tracker!$D11+1)))</f>
-        <v>0.3333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E6" s="50">
         <f>MAX(0,MIN(1,(E$3-Tracker!$D11+1)/(Tracker!$E11-Tracker!$D11+1)))</f>
-        <v>0.6666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="F6" s="50">
         <f>MAX(0,MIN(1,(F$3-Tracker!$D11+1)/(Tracker!$E11-Tracker!$D11+1)))</f>
@@ -18012,11 +17963,11 @@
       </c>
       <c r="I20" s="50">
         <f>MAX(0,MIN(1,(I$3-Tracker!$D25+1)/(Tracker!$E25-Tracker!$D25+1)))</f>
-        <v>0.3333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="J20" s="50">
         <f>MAX(0,MIN(1,(J$3-Tracker!$D25+1)/(Tracker!$E25-Tracker!$D25+1)))</f>
-        <v>0.6666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="K20" s="50">
         <f>MAX(0,MIN(1,(K$3-Tracker!$D25+1)/(Tracker!$E25-Tracker!$D25+1)))</f>
@@ -18144,11 +18095,11 @@
       </c>
       <c r="I22" s="50">
         <f>MAX(0,MIN(1,(I$3-Tracker!$D27+1)/(Tracker!$E27-Tracker!$D27+1)))</f>
-        <v>0.3333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="J22" s="50">
         <f>MAX(0,MIN(1,(J$3-Tracker!$D27+1)/(Tracker!$E27-Tracker!$D27+1)))</f>
-        <v>0.6666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="K22" s="50">
         <f>MAX(0,MIN(1,(K$3-Tracker!$D27+1)/(Tracker!$E27-Tracker!$D27+1)))</f>
@@ -18354,11 +18305,11 @@
       </c>
       <c r="L25" s="50">
         <f>MAX(0,MIN(1,(L$3-Tracker!$D30+1)/(Tracker!$E30-Tracker!$D30+1)))</f>
-        <v>0.3333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="M25" s="50">
         <f>MAX(0,MIN(1,(M$3-Tracker!$D30+1)/(Tracker!$E30-Tracker!$D30+1)))</f>
-        <v>0.6666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="N25" s="50">
         <f>MAX(0,MIN(1,(N$3-Tracker!$D30+1)/(Tracker!$E30-Tracker!$D30+1)))</f>
